--- a/template/t8_ocr_report.xlsx
+++ b/template/t8_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
   <si>
     <t>filename</t>
   </si>
@@ -40,18 +40,6 @@
     <t>black_radio</t>
   </si>
   <si>
-    <t>color_blue</t>
-  </si>
-  <si>
-    <t>color_green</t>
-  </si>
-  <si>
-    <t>color_yellow</t>
-  </si>
-  <si>
-    <t>color_red</t>
-  </si>
-  <si>
     <t>color_white</t>
   </si>
   <si>
@@ -64,6 +52,9 @@
     <t>green_centers</t>
   </si>
   <si>
+    <t>blue_centers</t>
+  </si>
+  <si>
     <t>micro_0020_XII0.jpg</t>
   </si>
   <si>
@@ -149,9 +140,6 @@
   </si>
   <si>
     <t>color_detection</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Yes</t>
@@ -486,10 +474,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,28 +517,19 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>0.6102314591407776</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -565,42 +544,33 @@
         <v>22.74085138162808</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -615,42 +585,33 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
+        <v>42</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>2</v>
       </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>0.9267359972000122</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -665,42 +626,33 @@
         <v>15.90739357729649</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>0.9446660280227661</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -715,42 +667,33 @@
         <v>22.47946228528753</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>0.9338569641113281</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -765,42 +708,33 @@
         <v>10.40462427745665</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M6" t="s">
-        <v>46</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>0.9935437440872192</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -815,42 +749,33 @@
         <v>9.392265193370166</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0.9965159296989441</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -865,42 +790,33 @@
         <v>14.12151067323481</v>
       </c>
       <c r="I8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M8" t="s">
-        <v>46</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>0.9838793873786926</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -915,42 +831,33 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
+        <v>42</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
         <v>2</v>
       </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -965,42 +872,33 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>0.9976737499237061</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1015,42 +913,33 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" t="s">
-        <v>45</v>
-      </c>
-      <c r="L11" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11" t="s">
-        <v>46</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>0.9660276770591736</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1065,42 +954,33 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M12" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>0.9935116171836853</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1115,98 +995,101 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" t="s">
-        <v>45</v>
-      </c>
-      <c r="L13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
       <c r="I14" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" t="s">
-        <v>46</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>42</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
       <c r="I15" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" t="s">
-        <v>45</v>
-      </c>
-      <c r="L15" t="s">
-        <v>45</v>
-      </c>
-      <c r="M15" t="s">
-        <v>46</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/template/t8_ocr_report.xlsx
+++ b/template/t8_ocr_report.xlsx
@@ -535,13 +535,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>22.74085138162808</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
         <v>42</v>
@@ -567,7 +567,7 @@
         <v>28</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.9927276372909546</v>
       </c>
       <c r="D3" t="s">
         <v>41</v>
@@ -617,13 +617,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15.90739357729649</v>
+        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>42</v>
@@ -649,7 +649,7 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>0.9446660280227661</v>
+        <v>0.9658370614051819</v>
       </c>
       <c r="D5" t="s">
         <v>41</v>
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>602</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>22.47946228528753</v>
+        <v>0</v>
       </c>
       <c r="I5" t="s">
         <v>42</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>10.40462427745665</v>
+        <v>0</v>
       </c>
       <c r="I6" t="s">
         <v>42</v>
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>9.392265193370166</v>
+        <v>0</v>
       </c>
       <c r="I7" t="s">
         <v>42</v>
@@ -784,10 +784,10 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>14.12151067323481</v>
+        <v>0</v>
       </c>
       <c r="I8" t="s">
         <v>42</v>
@@ -854,7 +854,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.8956170082092285</v>
       </c>
       <c r="D10" t="s">
         <v>41</v>
@@ -895,7 +895,7 @@
         <v>36</v>
       </c>
       <c r="C11">
-        <v>0.9976737499237061</v>
+        <v>0.9970347285270691</v>
       </c>
       <c r="D11" t="s">
         <v>41</v>
@@ -1080,13 +1080,13 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>1</v>

--- a/template/t8_ocr_report.xlsx
+++ b/template/t8_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
   <si>
     <t>filename</t>
   </si>
@@ -55,13 +55,16 @@
     <t>blue_centers</t>
   </si>
   <si>
-    <t>micro_0020_XII0.jpg</t>
+    <t>white_centers</t>
+  </si>
+  <si>
+    <t>micro_0021_XII0.jpg</t>
   </si>
   <si>
     <t>micro_0003_XF.jpg</t>
   </si>
   <si>
-    <t>micro_0019_X30.jpg</t>
+    <t>micro_0024_X30.jpg</t>
   </si>
   <si>
     <t>micro_0007_X10.jpg</t>
@@ -76,22 +79,22 @@
     <t>micro_0004_S1.jpg</t>
   </si>
   <si>
-    <t>micro_0017_S.jpg</t>
-  </si>
-  <si>
-    <t>micro_0009_FXII.jpg</t>
-  </si>
-  <si>
-    <t>micro_0016_FXF.jpg</t>
-  </si>
-  <si>
-    <t>micro_0022_FSI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0012_FS.jpg</t>
-  </si>
-  <si>
-    <t>micro_0018_D2.jpg</t>
+    <t>micro_0018_S.jpg</t>
+  </si>
+  <si>
+    <t>micro_0022_FXII.jpg</t>
+  </si>
+  <si>
+    <t>micro_0017_FXF.jpg</t>
+  </si>
+  <si>
+    <t>micro_0023_FSI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0013_FS.jpg</t>
+  </si>
+  <si>
+    <t>micro_0019_D2.jpg</t>
   </si>
   <si>
     <t>micro_0002_D1.jpg</t>
@@ -474,10 +477,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,19 +520,22 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2">
-        <v>0.6102314591407776</v>
+        <v>0.6100947260856628</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -544,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -558,19 +564,22 @@
       <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>0.9927276372909546</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -585,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -599,19 +608,22 @@
       <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>0.9267359972000122</v>
+        <v>0.9600300788879395</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -626,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -640,19 +652,22 @@
       <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5">
-        <v>0.9658370614051819</v>
+        <v>0.9424858689308167</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -667,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -681,19 +696,22 @@
       <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6">
-        <v>0.9338569641113281</v>
+        <v>0.9219494462013245</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -708,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -722,19 +740,22 @@
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>0.9935437440872192</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -749,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -763,19 +784,22 @@
       <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>0.9965159296989441</v>
+        <v>0.9970804452896118</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -790,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -804,19 +828,22 @@
       <c r="M8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9">
-        <v>0.9838793873786926</v>
+        <v>0.9883533120155334</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -831,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -845,224 +872,242 @@
       <c r="M9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10">
-        <v>0.8956170082092285</v>
+        <v>0.914544939994812</v>
       </c>
       <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11">
+        <v>0.9958702921867371</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>0.9482880234718323</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13">
+        <v>0.9928543567657471</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14">
+        <v>0.9976885914802551</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>41</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11">
-        <v>0.9970347285270691</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12">
-        <v>0.9660276770591736</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13">
-        <v>0.9935116171836853</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>2</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
       <c r="C15">
-        <v>1</v>
+        <v>0.9962726831436157</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1077,18 +1122,21 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
         <v>1</v>
       </c>
     </row>

--- a/template/t8_ocr_report.xlsx
+++ b/template/t8_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>filename</t>
   </si>
@@ -58,13 +58,19 @@
     <t>white_centers</t>
   </si>
   <si>
+    <t>is_tri</t>
+  </si>
+  <si>
+    <t>is_double</t>
+  </si>
+  <si>
     <t>micro_0021_XII0.jpg</t>
   </si>
   <si>
     <t>micro_0003_XF.jpg</t>
   </si>
   <si>
-    <t>micro_0024_X30.jpg</t>
+    <t>micro_0020_X30.jpg</t>
   </si>
   <si>
     <t>micro_0007_X10.jpg</t>
@@ -477,10 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,19 +529,25 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>0.6100947260856628</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -550,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -567,19 +579,25 @@
       <c r="N2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>0.9927276372909546</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -594,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -611,19 +629,25 @@
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4">
-        <v>0.9600300788879395</v>
+        <v>0.9442859292030334</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -638,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -655,19 +679,25 @@
       <c r="N4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5">
-        <v>0.9424858689308167</v>
+        <v>0.9689009189605713</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -682,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -699,19 +729,25 @@
       <c r="N5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>0.9219494462013245</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -726,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -743,19 +779,25 @@
       <c r="N6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>0.9935437440872192</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -770,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -785,21 +827,27 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>0.9970804452896118</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -814,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -831,19 +879,25 @@
       <c r="N8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>0.9883533120155334</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -858,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -875,19 +929,25 @@
       <c r="N9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10">
-        <v>0.914544939994812</v>
+        <v>0.9040690660476685</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -902,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -919,19 +979,25 @@
       <c r="N10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11">
-        <v>0.9958702921867371</v>
+        <v>0.9969213604927063</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -946,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -961,21 +1027,27 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>3</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>0.9482880234718323</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -990,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1007,63 +1079,75 @@
       <c r="N12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C13">
         <v>0.9928543567657471</v>
       </c>
       <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
         <v>42</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
       </c>
       <c r="C14">
         <v>0.9976885914802551</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1078,36 +1162,42 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
         <v>43</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>41</v>
       </c>
       <c r="C15">
         <v>0.9962726831436157</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1122,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1137,7 +1227,13 @@
         <v>1</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/template/t8_ocr_report.xlsx
+++ b/template/t8_ocr_report.xlsx
@@ -64,43 +64,43 @@
     <t>is_double</t>
   </si>
   <si>
-    <t>micro_0021_XII0.jpg</t>
+    <t>micro_0023_XⅡ.jpg</t>
   </si>
   <si>
     <t>micro_0003_XF.jpg</t>
   </si>
   <si>
-    <t>micro_0020_X30.jpg</t>
-  </si>
-  <si>
-    <t>micro_0007_X10.jpg</t>
-  </si>
-  <si>
-    <t>micro_0005_SII.jpg</t>
-  </si>
-  <si>
-    <t>micro_0006_S3.jpg</t>
-  </si>
-  <si>
-    <t>micro_0004_S1.jpg</t>
-  </si>
-  <si>
-    <t>micro_0018_S.jpg</t>
+    <t>micro_0025_X3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0012_X1.jpg</t>
+  </si>
+  <si>
+    <t>micro_0006_SⅡI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0007_S3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0005_S1.jpg</t>
+  </si>
+  <si>
+    <t>micro_0019_S.jpg</t>
   </si>
   <si>
     <t>micro_0022_FXII.jpg</t>
   </si>
   <si>
-    <t>micro_0017_FXF.jpg</t>
-  </si>
-  <si>
-    <t>micro_0023_FSI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0013_FS.jpg</t>
-  </si>
-  <si>
-    <t>micro_0019_D2.jpg</t>
+    <t>micro_0001_FXF.jpg</t>
+  </si>
+  <si>
+    <t>micro_0024_FSI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0014_FS.jpg</t>
+  </si>
+  <si>
+    <t>micro_0020_D2.jpg</t>
   </si>
   <si>
     <t>micro_0002_D1.jpg</t>
@@ -544,7 +544,7 @@
         <v>30</v>
       </c>
       <c r="C2">
-        <v>0.6100947260856628</v>
+        <v>0.8567864894866943</v>
       </c>
       <c r="D2" t="s">
         <v>44</v>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>0.9927276372909546</v>
+        <v>0.9950690269470215</v>
       </c>
       <c r="D3" t="s">
         <v>44</v>
@@ -627,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -644,7 +644,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>0.9442859292030334</v>
+        <v>0.8986022472381592</v>
       </c>
       <c r="D4" t="s">
         <v>44</v>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -694,7 +694,7 @@
         <v>33</v>
       </c>
       <c r="C5">
-        <v>0.9689009189605713</v>
+        <v>0.958402156829834</v>
       </c>
       <c r="D5" t="s">
         <v>44</v>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>34</v>
       </c>
       <c r="C6">
-        <v>0.9219494462013245</v>
+        <v>0.9544151425361633</v>
       </c>
       <c r="D6" t="s">
         <v>44</v>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>35</v>
       </c>
       <c r="C7">
-        <v>0.9935437440872192</v>
+        <v>0.989605724811554</v>
       </c>
       <c r="D7" t="s">
         <v>44</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -844,7 +844,7 @@
         <v>36</v>
       </c>
       <c r="C8">
-        <v>0.9970804452896118</v>
+        <v>0.9959807991981506</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>37</v>
       </c>
       <c r="C9">
-        <v>0.9883533120155334</v>
+        <v>0.9719192981719971</v>
       </c>
       <c r="D9" t="s">
         <v>44</v>
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>38</v>
       </c>
       <c r="C10">
-        <v>0.9040690660476685</v>
+        <v>0.9418363571166992</v>
       </c>
       <c r="D10" t="s">
         <v>44</v>
@@ -965,7 +965,7 @@
         <v>45</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>39</v>
       </c>
       <c r="C11">
-        <v>0.9969213604927063</v>
+        <v>0.9969632029533386</v>
       </c>
       <c r="D11" t="s">
         <v>44</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -1044,7 +1044,7 @@
         <v>40</v>
       </c>
       <c r="C12">
-        <v>0.9482880234718323</v>
+        <v>0.9877138733863831</v>
       </c>
       <c r="D12" t="s">
         <v>44</v>
@@ -1094,7 +1094,7 @@
         <v>41</v>
       </c>
       <c r="C13">
-        <v>0.9928543567657471</v>
+        <v>0.9913275241851807</v>
       </c>
       <c r="D13" t="s">
         <v>44</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -1144,7 +1144,7 @@
         <v>42</v>
       </c>
       <c r="C14">
-        <v>0.9976885914802551</v>
+        <v>0.9950766563415527</v>
       </c>
       <c r="D14" t="s">
         <v>44</v>
@@ -1165,19 +1165,19 @@
         <v>45</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         <v>43</v>
       </c>
       <c r="C15">
-        <v>0.9962726831436157</v>
+        <v>0.996875524520874</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -1227,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
